--- a/DataTables/Datas/#NounDictionary.xlsx
+++ b/DataTables/Datas/#NounDictionary.xlsx
@@ -1,316 +1,187 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>僵直</t>
-  </si>
-  <si>
-    <t>打出此牌后，需要休息{T}格才可以行动</t>
-  </si>
-  <si>
-    <t>引导</t>
-  </si>
-  <si>
-    <t>需持续占用 {T} 格时间。中途被打断,施法失败</t>
-  </si>
-  <si>
-    <t>推迟</t>
-  </si>
-  <si>
-    <t>将目标的行动向后推 {T} 格。</t>
-  </si>
-  <si>
-    <t>晕眩</t>
-  </si>
-  <si>
-    <t>目标无法行动，其当前时间格上的所有意图失效</t>
-  </si>
-  <si>
-    <t>嘲讽</t>
-  </si>
-  <si>
-    <r>
-      <t>敌人</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>必须优先攻击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>拥有此状态的角色，无法选取其他人</t>
-    </r>
-  </si>
-  <si>
-    <t>迅捷</t>
-  </si>
-  <si>
-    <r>
-      <t>此行动</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>不占用时间格</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>。你可以立即打出</t>
-    </r>
-  </si>
-  <si>
-    <t>拦截</t>
-  </si>
-  <si>
-    <t>当指定队友受到攻击时，由你代替其承受伤害。</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -610,162 +481,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -821,11 +692,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1077,121 +1011,325 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>19</v>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>僵直</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>打出此牌后，需要休息{T}格才可以行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>引导</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>需持续占用 {T} 格时间。中途被打断,施法失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>推迟</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>将目标的行动向后推 {T} 格。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>晕眩</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>目标无法行动，其当前时间格上的所有意图失效</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>嘲讽</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>敌人必须优先攻击拥有此状态的角色，无法选取其他人</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>迅捷</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>此行动不占用时间格。你可以立即打出</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>拦截</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>当指定队友受到攻击时，由你代替其承受伤害。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>中毒</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>每回合开始受到 {V} 点伤害，并衰减 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>燃烧</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>每回合开始受到 {V} 点伤害，持续 {T} 回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>寒冷</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>受击时 [推迟] 来源，持续 {T} 回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>虚弱</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>造成伤害降低 {V}%，持续 {T} 回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>脆弱</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>受到的伤害提高 {V}%，持续 {T} 回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>力量</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>攻击伤害 +{V}，持续 {T} 回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>敏捷</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>防御牌额外 +{V} 护甲，持续 {T} 回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>破韧</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>累计承受 {V} 点伤害后行动被打断</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>定身</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>无法移动，持续 {T} 回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>充能</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>下回合开始 +{V} 能量</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>圣物</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>接下来 {V} 次负面效果被自动抵消</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>灵感</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>新回合开始时多抽 {V} 张牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>减费</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>下一张牌费用 -{V}</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/DataTables/Datas/#NounDictionary.xlsx
+++ b/DataTables/Datas/#NounDictionary.xlsx
@@ -1016,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -1297,6 +1297,30 @@
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>下一张牌费用 -{V}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>虚无</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>回合结束时该牌会自毁，不会进入弃牌堆</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>一次性</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>使用后该牌会自毁，不会进入弃牌堆</t>
         </is>
       </c>
     </row>

--- a/DataTables/Datas/#NounDictionary.xlsx
+++ b/DataTables/Datas/#NounDictionary.xlsx
@@ -1016,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -1301,26 +1301,86 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>虚无</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>回合结束时该牌会自毁，不会进入弃牌堆</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>一次性</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>使用后该牌会自毁，不会进入弃牌堆</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>前排</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>只能在角色处于前排时打出此牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>后排</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>只能在角色处于后排时打出此牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>只能攻击处于前排的角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>远程</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>只能攻击处于后排的角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>过载</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>使用后自身过载：下一次行动推迟 {V} 格</t>
         </is>
       </c>
     </row>
